--- a/Output Data Tables/AFAT Outputs/Aggregated Tables/2016/Airline_Cumulative_Financial_Statistics_2016.xlsx
+++ b/Output Data Tables/AFAT Outputs/Aggregated Tables/2016/Airline_Cumulative_Financial_Statistics_2016.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44" uniqueCount="44">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -178,7 +190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -204,49 +216,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1404,48 +1416,248 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>83240418930</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0.121</v>
+      </c>
+      <c r="D25" s="0">
+        <v>177.97</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="F25" s="0">
+        <v>214.08000000000001</v>
+      </c>
+      <c r="G25" s="0">
+        <v>91172649950</v>
+      </c>
+      <c r="H25" s="0">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="I25" s="0">
+        <v>194.91999999999999</v>
+      </c>
+      <c r="J25" s="0">
+        <v>0.1588</v>
+      </c>
+      <c r="K25" s="0">
+        <v>234.49000000000001</v>
+      </c>
+      <c r="L25" s="0">
+        <v>274292</v>
+      </c>
+      <c r="M25" s="0">
+        <v>2508841</v>
+      </c>
+      <c r="N25" s="0">
+        <v>122166</v>
+      </c>
+      <c r="O25" s="0">
+        <v>332393</v>
+      </c>
+      <c r="P25" s="0">
+        <v>20.539999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>27321961780</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0.1053</v>
+      </c>
+      <c r="D26" s="0">
+        <v>96.450000000000003</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0.12479999999999999</v>
+      </c>
+      <c r="F26" s="0">
+        <v>118.52</v>
+      </c>
+      <c r="G26" s="0">
+        <v>33647119790</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0.12970000000000001</v>
+      </c>
+      <c r="I26" s="0">
+        <v>118.78</v>
+      </c>
+      <c r="J26" s="0">
+        <v>0.1537</v>
+      </c>
+      <c r="K26" s="0">
+        <v>145.96000000000001</v>
+      </c>
+      <c r="L26" s="0">
+        <v>85033</v>
+      </c>
+      <c r="M26" s="0">
+        <v>3050110</v>
+      </c>
+      <c r="N26" s="0">
+        <v>128076</v>
+      </c>
+      <c r="O26" s="0">
+        <v>395695</v>
+      </c>
+      <c r="P26" s="0">
+        <v>23.809999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>4849379390</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0.079299999999999995</v>
+      </c>
+      <c r="D27" s="0">
+        <v>80.170000000000002</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0.093600000000000003</v>
+      </c>
+      <c r="F27" s="0">
+        <v>95.379999999999995</v>
+      </c>
+      <c r="G27" s="0">
+        <v>5450043190</v>
+      </c>
+      <c r="H27" s="0">
+        <v>0.089099999999999999</v>
+      </c>
+      <c r="I27" s="0">
+        <v>90.109999999999999</v>
+      </c>
+      <c r="J27" s="0">
+        <v>0.1052</v>
+      </c>
+      <c r="K27" s="0">
+        <v>107.19</v>
+      </c>
+      <c r="L27" s="0">
+        <v>14420</v>
+      </c>
+      <c r="M27" s="0">
+        <v>4242225</v>
+      </c>
+      <c r="N27" s="0">
+        <v>87659</v>
+      </c>
+      <c r="O27" s="0">
+        <v>377950</v>
+      </c>
+      <c r="P27" s="0">
+        <v>48.390000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>5880407010</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.0877</v>
+      </c>
+      <c r="D28" s="0">
+        <v>42.780000000000001</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0.1094</v>
+      </c>
+      <c r="F28" s="0">
+        <v>54.420000000000002</v>
+      </c>
+      <c r="G28" s="0">
+        <v>6265178400</v>
+      </c>
+      <c r="H28" s="0">
+        <v>0.093399999999999997</v>
+      </c>
+      <c r="I28" s="0">
+        <v>45.579999999999998</v>
+      </c>
+      <c r="J28" s="0">
+        <v>0.11650000000000001</v>
+      </c>
+      <c r="K28" s="0">
+        <v>57.979999999999997</v>
+      </c>
+      <c r="L28" s="0">
+        <v>41218</v>
+      </c>
+      <c r="M28" s="0">
+        <v>1627135</v>
+      </c>
+      <c r="N28" s="0">
+        <v>64958</v>
+      </c>
+      <c r="O28" s="0">
+        <v>152001</v>
+      </c>
+      <c r="P28" s="0">
+        <v>25.050000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>121292167110</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>0.1128</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>127.81999999999999</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>0.13500000000000001</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>155.84999999999999</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>136534991330</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>0.12690000000000001</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>143.88</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>0.15190000000000001</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>175.44</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>414963</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>2592413</v>
       </c>
-      <c r="N25" s="0">
+      <c r="N29" s="0">
         <v>116496</v>
       </c>
-      <c r="O25" s="0">
+      <c r="O29" s="0">
         <v>329029</v>
       </c>
-      <c r="P25" s="0">
+      <c r="P29" s="0">
         <v>22.25</v>
       </c>
     </row>
